--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_nuble.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_nuble.xlsx
@@ -375,286 +375,286 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="C2">
-        <v>160048</v>
+        <v>95.55904892906268</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Ninhue</t>
         </is>
       </c>
       <c r="C3">
-        <v>49898</v>
+        <v>95.06240822320117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>San Ignacio</t>
         </is>
       </c>
       <c r="C4">
-        <v>26885</v>
+        <v>94.36423505572442</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>Pemuco</t>
         </is>
       </c>
       <c r="C5">
-        <v>25254</v>
+        <v>94.16130628401781</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="C6">
-        <v>20314</v>
+        <v>93.3984244979474</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quillón</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="C7">
-        <v>17378</v>
+        <v>93.25045820384095</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yungay</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="C8">
-        <v>15913</v>
+        <v>93.11233253177602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>Treguaco</t>
         </is>
       </c>
       <c r="C9">
-        <v>14902</v>
+        <v>92.56008359456635</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Coelemu</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="C10">
-        <v>14846</v>
+        <v>92.34486461609266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="C11">
-        <v>12039</v>
+        <v>91.87167880338517</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="C12">
-        <v>11702</v>
+        <v>91.60718148388493</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="C13">
-        <v>11326</v>
+        <v>91.52573461975861</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="C14">
-        <v>10842</v>
+        <v>91.33751691891227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pemuco</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="C15">
-        <v>7612</v>
+        <v>91.15492957746478</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ninhue</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="C16">
-        <v>5179</v>
+        <v>90.97215172740501</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
+          <t>Quillón</t>
         </is>
       </c>
       <c r="C17">
-        <v>4863</v>
+        <v>90.86535947712419</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="C18">
-        <v>4668</v>
+        <v>90.57428214731586</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Treguaco</t>
+          <t>Yungay</t>
         </is>
       </c>
       <c r="C19">
-        <v>4429</v>
+        <v>88.46453191016234</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="C20">
-        <v>4235</v>
+        <v>83.51274491899085</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +710,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_nuble.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C647"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -655,6 +655,9411 @@
       </c>
       <c r="C20">
         <v>83.51274491899085</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>50.53230543318649</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>49.00766358813127</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>48.60872552387496</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>48.57535861662409</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>48.54032657100446</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>48.25624082232012</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>48.21893686488866</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>48.19507530480517</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>48.15729483282675</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>48.01881365681995</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>47.83699059561128</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>47.79739611200285</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>47.41192678606573</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>47.17607973421927</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>47.09063378758382</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>47.06165168830209</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>46.98369031243859</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>46.80616740088106</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>46.67484850809235</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>46.33677280964532</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>46.29376257545272</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>46.2797385620915</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>46.20694022289767</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>46.14743162108072</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>45.6700161080003</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>45.62097971301336</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>45.35022710972986</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>45.24407106890344</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>45.05538289903578</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>44.86116700201207</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>44.72309299895507</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>44.69254551700447</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>44.58586626139817</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>44.58562091503268</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>44.5165476963011</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>44.50360700790107</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>44.45975201731942</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>44.161437184693</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>43.7635276422466</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>43.49160082841144</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>43.48095002474022</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>43.30679775486995</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>42.95333807058505</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>42.77688603531301</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>42.31710028908161</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>42.13714038503137</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>41.73458725182863</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>41.48082399497023</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>40.91750503018109</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>40.77937413894902</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>40.64116283217407</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>39.85882352941177</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>38.65510028300726</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>38.2686738500874</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>38.10442256285318</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>37.69834850896189</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>37.5138981543251</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>31.70635701633537</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>27.86220871327254</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>27.61973065582915</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>26.62080698250675</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>26.47631408176509</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>26.1327967806841</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>24.33201385452746</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>24.14117647058823</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>23.73747298093928</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>23.6417033773862</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>22.5914315569488</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>22.1830985915493</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>21.81297919953043</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>20.84235386734895</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>20.38882736557155</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>20.37631532013555</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>20.28018679119413</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>20.22760646108664</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>19.80742778541953</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>19.72846513768505</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>19.71373464622881</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>19.29371231696813</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>19.11481067911887</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>18.74608150470219</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>18.21440684599128</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>18.03424505225706</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>17.9663345929234</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>17.7359477124183</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>17.67250703006706</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>17.53396029258098</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>17.11578688322874</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>17.10486245051264</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>16.96540039236669</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>16.62234042553191</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>16.60690094828273</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>16.43182070342838</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>16.3313865455332</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>16.10800030681905</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>16.06070713809206</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>15.88555649305822</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>15.72241464621474</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>15.6612301041462</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>15.62173038229376</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>15.58319957196362</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>15.57397328055418</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>15.54923305294409</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>15.50863934847206</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>15.38140020898642</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>15.23627380667782</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>15.14178705189941</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>15.13202614379085</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>14.84929078014184</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>14.77493671814814</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>14.73760284634201</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>14.72253385165279</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>14.68428781204112</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>14.66121281044792</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>14.49720027613715</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>14.3843137254902</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>14.37650291995878</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>14.1749723145072</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>14.16781292984869</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>14.16180006870491</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>14.04426559356137</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>14.03918383920414</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>14.03267073410746</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>13.89029878523331</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>13.75556655121227</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>13.67048111234158</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>13.66432727177855</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>13.62082066869301</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>13.61736750619476</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>13.59475507174666</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>13.56461086637298</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>13.44869215291751</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>13.44075456867754</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>13.41765597840157</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>13.35478383076297</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>13.32468094311053</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>13.29154002026342</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>13.28237105064051</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>13.20088977525504</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>13.1999312950876</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>13.18986228132508</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>13.1778783462453</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>13.12455175711212</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>13.10699360183439</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>13.05151817744739</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>13.02213279678068</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>13.01679834317711</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>12.99987695336532</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>12.99559471365639</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>12.97314527053948</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>12.94618291206574</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>12.93360160965795</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>12.9225459344229</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>12.87745571238488</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>12.86727456940223</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>12.83623366119648</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>12.8154379020287</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>12.80542179418584</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>12.77307616610903</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>12.73725490196078</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>12.71178883538434</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>12.70182068017863</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>12.68388422172493</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>12.66800804828974</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>12.63620191238603</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>12.63248972528661</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>12.60134267581349</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>12.59140360263956</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>12.45817752410943</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>12.45559038662487</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>12.38791324061855</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>12.38123188671631</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>12.37151248164464</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>12.28758169934641</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>12.20480668756531</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>12.196057375163</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>12.19392149624708</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>12.18590171225261</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>12.16760974888125</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>12.15172239108409</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>12.10453920220083</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>12.09658140090844</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>12.08901875864228</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>12.05635812377385</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>12.04849084611578</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>12.03024238381143</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>12.01671891327064</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>11.98501872659176</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>11.89542483660131</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>11.86804245719146</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>11.86018550326348</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>11.85159738921333</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>11.83566822325995</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>11.82787451100713</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>11.76895708249944</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>11.74595585305602</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>11.73864894795127</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>11.73333333333333</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>11.71403962101637</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>11.67942601427568</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>11.63293377873846</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>11.61971830985915</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>11.611130195809</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>11.59591953873046</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>11.55940783922682</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>11.50905432595573</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>11.49425287356322</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>11.46704916726432</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>11.35613682092555</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>11.33463119186675</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>11.32525697503671</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>11.31300021630975</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>11.28888888888889</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>11.17429105983345</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>11.1322188449848</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>11.11116908867959</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>11.07505948518278</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>11.06861104470476</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>10.99719148648191</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>10.9612462006079</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>10.92304664436135</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>10.82384957941613</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>10.7839412360689</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>10.74324076451814</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>10.72966654362003</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>10.70937315779132</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>10.70010449320794</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>10.65593561368209</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>10.62782916748671</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>10.62775330396476</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>10.62592775853538</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>10.61112202790332</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>10.59104258443466</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>10.56849904771844</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>10.55591607181484</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>10.5359477124183</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>10.47947754881061</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>10.45422526024681</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>10.39165518598701</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>10.36123729180186</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>10.29070804351703</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>10.26123301985371</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>10.23776773432894</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>10.21452469986223</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>9.845452523904825</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>9.563142437591777</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>9.211889393577177</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>8.994292462113757</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>7.571714476317545</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>6.734326489081375</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>5.354692269560907</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>5.278651913511319</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>5.167958656330749</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>5.018697106868727</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>4.715873656407058</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>4.705882352941177</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>4.580831665554815</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>4.538969145710719</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>4.490945674044266</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>4.263953746942406</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>3.828682673588579</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>3.718653383716936</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>3.506483341595137</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>3.343782654127482</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>3.290450272142504</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>3.289006192264745</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>3.273050038832797</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>3.198588632354069</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>3.014642549526271</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>2.990882810762731</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>2.853768943121433</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>2.849673202614379</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>2.823449607346917</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>2.804530051721063</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>2.767893172897025</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>2.669535421149095</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>2.516110516841034</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>2.48692152917505</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>2.464452503326463</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>2.278146667155802</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>2.273302938196555</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>2.164928163747294</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>2.153316106804479</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>2.141466580142764</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>2.117456755981111</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>2.102574179603065</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>2.084390755591649</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>2.078179119247897</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>2.068965517241379</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>2.018206801786328</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>2.004024144869215</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>1.989645721246574</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>1.963641942164609</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>1.947980483510033</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>1.945263377599207</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>1.89621435466618</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>1.871370982654684</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>1.856209150326797</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>1.823613340467273</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>1.734439093989656</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>1.70704845814978</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>1.700446581930608</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>1.689060502491586</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>1.687216093445814</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C325">
+        <v>1.633596302494223</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>1.538260846878343</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>1.521523998020782</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>1.456526573271069</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>1.456406219248179</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>1.445408049810985</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>1.411367645930812</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>1.401679056178113</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>1.390426971822321</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>1.38677811550152</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>1.380392156862745</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>1.367578385590394</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>1.365510133974579</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>1.359665313153685</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>1.336215366476714</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>1.318062041796029</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>1.316614420062696</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>1.311800464400324</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>1.279275733123401</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>1.274817136886102</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>1.272290461205292</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>1.261952412719591</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>1.236618678479144</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>1.234946690189461</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>1.232965606748864</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>1.218150441579535</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>1.215291750503018</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>1.212271152894607</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>1.209364251636525</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>1.156387665198238</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>1.140324163367509</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>1.106293084278408</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>1.102145246998622</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>1.095115048603421</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C359">
+        <v>1.052256108435884</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C360">
+        <v>1.035939118654873</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C361">
+        <v>1.028463420057816</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C362">
+        <v>1.024033437826541</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C363">
+        <v>1.016178142998643</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C364">
+        <v>1.01437908496732</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C365">
+        <v>0.98405825624877</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C366">
+        <v>0.9815096251266464</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C367">
+        <v>0.9728708027573938</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C368">
+        <v>0.970321728603397</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C369">
+        <v>0.96579476861167</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C370">
+        <v>0.9642202565941509</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C371">
+        <v>0.9541644373105047</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C372">
+        <v>0.9432108469247397</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C373">
+        <v>0.9416498993963782</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C374">
+        <v>0.9301319489508977</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C375">
+        <v>0.9255533199195171</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C376">
+        <v>0.9250147608738437</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C377">
+        <v>0.9045751633986928</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C378">
+        <v>0.9017519752662315</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C379">
+        <v>0.8941176470588236</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C380">
+        <v>0.8933601609657947</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C381">
+        <v>0.8920881013904269</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C382">
+        <v>0.8865248226950354</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C383">
+        <v>0.8845757471659224</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C384">
+        <v>0.8810572687224669</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C385">
+        <v>0.8459378066524549</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C386">
+        <v>0.8426966292134831</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C387">
+        <v>0.8418300653594771</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C388">
+        <v>0.8290190505194058</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C389">
+        <v>0.8287976249381495</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C390">
+        <v>0.8164275111331024</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C391">
+        <v>0.809308878394949</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C392">
+        <v>0.8072827207145311</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C393">
+        <v>0.7936507936507936</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C394">
+        <v>0.7872466049990159</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C395">
+        <v>0.7823885863312112</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C396">
+        <v>0.7782966422059151</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C397">
+        <v>0.7751937984496124</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C398">
+        <v>0.7714952796670389</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C399">
+        <v>0.7663588131263509</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C400">
+        <v>0.7570841444949167</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C401">
+        <v>0.7440362046483087</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C402">
+        <v>0.7354531689379191</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C403">
+        <v>0.7321274763135228</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C404">
+        <v>0.73003411717231</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C405">
+        <v>0.7215686274509804</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C406">
+        <v>0.7085219444991143</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C407">
+        <v>0.7082494969818913</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C408">
+        <v>0.7080230382625922</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C409">
+        <v>0.7063870705277562</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C410">
+        <v>0.6911004102015338</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C411">
+        <v>0.6896551724137931</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C412">
+        <v>0.6797385620915033</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C413">
+        <v>0.6732655609060103</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C414">
+        <v>0.6705602422669262</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C415">
+        <v>0.6693760459000717</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C416">
+        <v>0.6687565308254964</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C417">
+        <v>0.6680080482897385</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C418">
+        <v>0.6679861454725383</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C419">
+        <v>0.6657050926439587</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C420">
+        <v>0.6535947712418301</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C421">
+        <v>0.6534385209976891</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C422">
+        <v>0.6521471637750708</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C423">
+        <v>0.650971999286606</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C424">
+        <v>0.6494784491241882</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C425">
+        <v>0.6454697585464977</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C426">
+        <v>0.644874360684901</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C427">
+        <v>0.6398165612633603</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C428">
+        <v>0.639564336372847</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C429">
+        <v>0.6361452306026461</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C430">
+        <v>0.6355204397114393</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C431">
+        <v>0.6309842620785796</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C432">
+        <v>0.6297972839992128</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C433">
+        <v>0.6144759528962911</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C434">
+        <v>0.6061355764473033</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C435">
+        <v>0.596078431372549</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C436">
+        <v>0.5955734406438632</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C437">
+        <v>0.5840363400389358</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C438">
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C439">
+        <v>0.5698565533503636</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C440">
+        <v>0.5647058823529412</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C441">
+        <v>0.5647058823529412</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C442">
+        <v>0.5522742962337961</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C443">
+        <v>0.5510726234993112</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C444">
+        <v>0.5506607929515418</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C445">
+        <v>0.5407743889249406</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C446">
+        <v>0.5350454788657036</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C447">
+        <v>0.5292628672240546</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C448">
+        <v>0.5288657124893672</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C449">
+        <v>0.5261280542179418</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C450">
+        <v>0.5238749570594298</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C451">
+        <v>0.522466039707419</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C452">
+        <v>0.5214689892377676</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C453">
+        <v>0.5167958656330749</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C454">
+        <v>0.5150905432595574</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C455">
+        <v>0.5139219145508936</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C456">
+        <v>0.511757584650941</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C457">
+        <v>0.5109464352180828</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C458">
+        <v>0.5109058754175673</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C459">
+        <v>0.5103739043603683</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C460">
+        <v>0.5015673981191222</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C461">
+        <v>0.4967320261437909</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C462">
+        <v>0.4952492754686526</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C463">
+        <v>0.4909456740442656</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C464">
+        <v>0.4904583556268949</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C465">
+        <v>0.487260176631814</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C466">
+        <v>0.4807870113539702</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C467">
+        <v>0.4772393538913363</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C468">
+        <v>0.4758814622539477</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C469">
+        <v>0.4714039399831249</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C470">
+        <v>0.4659011702556954</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C471">
+        <v>0.4637581587083476</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C472">
+        <v>0.4568064155923257</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C473">
+        <v>0.4542194597179058</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C474">
+        <v>0.4495947315096251</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C475">
+        <v>0.4391816766733378</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C476">
+        <v>0.438871473354232</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C477">
+        <v>0.4369300911854103</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C478">
+        <v>0.4326195111399524</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C479">
+        <v>0.4326195111399524</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C480">
+        <v>0.4323049715071723</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C481">
+        <v>0.4218761985119276</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C482">
+        <v>0.4208175884575747</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C483">
+        <v>0.4205838693715982</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C484">
+        <v>0.4179728317659352</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C485">
+        <v>0.407204959829781</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C486">
+        <v>0.4036413603572656</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C487">
+        <v>0.3930045195519749</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C488">
+        <v>0.3782696177062374</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C489">
+        <v>0.375292235757352</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C490">
+        <v>0.3745318352059925</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C491">
+        <v>0.3736068895643364</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C492">
+        <v>0.3736068895643364</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C493">
+        <v>0.3733542935743761</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C494">
+        <v>0.3692889041566472</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C495">
+        <v>0.3677265844689596</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C496">
+        <v>0.3661378009541773</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C497">
+        <v>0.3611556982343499</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C498">
+        <v>0.3605123878192836</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C499">
+        <v>0.3587410777025777</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C500">
+        <v>0.3585943103036098</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C501">
+        <v>0.3566969859104691</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C502">
+        <v>0.3552769070010449</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C503">
+        <v>0.3542609722495572</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C504">
+        <v>0.3487518355359765</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C505">
+        <v>0.3460956089119619</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C506">
+        <v>0.3426567854012272</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C507">
+        <v>0.3345798071245818</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C508">
+        <v>0.3199212501538083</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C509">
+        <v>0.3092528451261752</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C510">
+        <v>0.3092528451261752</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C511">
+        <v>0.3032656533155812</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C512">
+        <v>0.3028129731452706</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C513">
+        <v>0.2991485771266396</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C514">
+        <v>0.2991485771266396</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C515">
+        <v>0.2968827313211281</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C516">
+        <v>0.2936857562408223</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C517">
+        <v>0.2912867274569402</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C518">
+        <v>0.2845126175160811</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C519">
+        <v>0.2838076244534786</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C520">
+        <v>0.2748196496049468</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C521">
+        <v>0.2659574468085106</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C522">
+        <v>0.2597723899059871</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C523">
+        <v>0.2569750367107195</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C524">
+        <v>0.2507836990595611</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C525">
+        <v>0.2334889926617745</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C526">
+        <v>0.2202643171806167</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C527">
+        <v>0.2199438297296383</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C528">
+        <v>0.2151565861821659</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C529">
+        <v>0.2089665653495441</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C530">
+        <v>0.2019089574155653</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C531">
+        <v>0.1992190612797833</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C532">
+        <v>0.1975266231535555</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C533">
+        <v>0.1965022597759874</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C534">
+        <v>0.1880877742946709</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C535">
+        <v>0.1855517070757051</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C536">
+        <v>0.183553597650514</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C537">
+        <v>0.1812197196641888</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C538">
+        <v>0.1771304861247786</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C539">
+        <v>0.1768520337983887</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C540">
+        <v>0.1671891327063741</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C541">
+        <v>0.1646403242147923</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C542">
+        <v>0.1583080040526849</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C543">
+        <v>0.1572018078207899</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C544">
+        <v>0.15340952673161</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C545">
+        <v>0.1519756838905775</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C546">
+        <v>0.14765596160945</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C547">
+        <v>0.1468428781204112</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C548">
+        <v>0.1468428781204112</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C549">
+        <v>0.145997938852628</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C550">
+        <v>0.1455816744501552</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C551">
+        <v>0.1375515818431912</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C552">
+        <v>0.1375515818431912</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C553">
+        <v>0.1354689616702526</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C554">
+        <v>0.1179013558655925</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C555">
+        <v>0.1101321585903084</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C556">
+        <v>0.1000667111407605</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C557">
+        <v>0.09177679882525698</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C558">
+        <v>0.08652390222799049</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C559">
+        <v>0.08557489107464322</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C560">
+        <v>0.08359456635318704</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C561">
+        <v>0.0825415459114421</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C562">
+        <v>0.07872466049990159</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C563">
+        <v>0.07579810950597468</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C564">
+        <v>0.07422068283028203</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C565">
+        <v>0.05895067793279623</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C566">
+        <v>0.05633802816901409</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C567">
+        <v>0.04921865386981666</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C568">
+        <v>0.04807870113539702</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C569">
+        <v>0.04432624113475177</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C570">
+        <v>0.04398876594592765</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C571">
+        <v>0.04326195111399524</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C572">
+        <v>0.04183006535947712</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C573">
+        <v>0.04179728317659352</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C574">
+        <v>0.04024144869215292</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C575">
+        <v>0.03671071953010279</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C576">
+        <v>0.03668513151619648</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C577">
+        <v>0.03660130718954249</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C578">
+        <v>0.03566969859104691</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C579">
+        <v>0.0333555703802535</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C580">
+        <v>0.03068190534632201</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C581">
+        <v>0.02707000981287856</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C582">
+        <v>0.02576434215046376</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C583">
+        <v>0.02163097555699762</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C584">
+        <v>0.02091503267973856</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C585">
+        <v>0.02089864158829676</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C586">
+        <v>0.0196811651249754</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C587">
+        <v>0.0183553597650514</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C588">
+        <v>0.01717622810030917</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C589">
+        <v>0.01609657947686117</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C590">
+        <v>0.01593752490238266</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C591">
+        <v>0.01479344650319908</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C592">
+        <v>0.01353500490643928</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C593">
+        <v>0.01283979603066877</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C594">
+        <v>0.0111185234600845</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C595">
+        <v>0.01109508487739931</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C596">
+        <v>0.0109577604424848</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C597">
+        <v>0.008917424647761726</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C598">
+        <v>0.00796876245119133</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C599">
+        <v>0.007670476336580502</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C600">
+        <v>0.007670476336580502</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C601">
+        <v>0.006332320162107396</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C614">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C615">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C618">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C622">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C626">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C629">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C631">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C635">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C639">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C641">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C642">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C643">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C644">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C645">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C646">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C647">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
